--- a/design/デザイン案.xlsx
+++ b/design/デザイン案.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="225">
   <si>
     <r>
       <rPr>
@@ -72,7 +72,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">v1</t>
+      <t xml:space="preserve">v2</t>
     </r>
     <r>
       <rPr>
@@ -1565,6 +1565,14 @@
     <r>
       <rPr>
         <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">通勤電車の中でスマホで勉強。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -1594,6 +1602,351 @@
         <rFont val="游ゴシック体"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">問の○</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に答えると、すぐに正解と簡単な解説。苦手なテーマは正答率でひと目でわかり、繰り返すほど弱点をカバーできます。まずは無料でお試しください。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">審査なしでいつでも変えられる欄</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：通勤電車・回答直後の解説・正答率・繰り返しで弱点カバーの要素を入れた</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">T4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">キーワード</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">宅建士</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">宅地建物取引士</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">過去問</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">模試</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">一問一答</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,○×,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不動産</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資格</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">試験対策</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">問題集</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">勉強</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">宅建業法</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">権利関係</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">法令上の制限</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">スキマ時間</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">カンマ区切り・空白なし。アプリ名に入っている「宅建」「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分」は入れなくてよい</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">T5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">説明文</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">問・</t>
     </r>
     <r>
@@ -1611,24 +1964,26 @@
         <rFont val="游ゴシック体"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">分。本試験と同じ分野比率で出題し、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回で本試験</t>
+      <t xml:space="preserve">分。通勤や昼休みに、本試験と同じ分野比率の○</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">模試を。
+■ 通勤電車の中で、スマホで勉強
+・</t>
     </r>
     <r>
       <rPr>
@@ -1645,274 +2000,7 @@
         <rFont val="游ゴシック体"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">回分。間違えた論点は、その場で解説と類題</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">問で復習できます。まずは無料でお試しください。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">審査なしでいつでも変えられる欄</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">キーワード</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">宅建士</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">宅地建物取引士</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">過去問</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模試</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">一問一答</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,○×,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">不動産</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">資格</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">試験対策</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">問題集</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">勉強</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">宅建業法</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">権利関係</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">法令上の制限</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">スキマ時間</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">カンマ区切り・空白なし。アプリ名に入っている「宅建」「</t>
+      <t xml:space="preserve">回は</t>
     </r>
     <r>
       <rPr>
@@ -1929,66 +2017,7 @@
         <rFont val="游ゴシック体"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">分」は入れなくてよい</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">T5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">説明文</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">問・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">分。通勤や昼休みに、本試験と同じ分野比率の○</t>
+      <t xml:space="preserve">問の○</t>
     </r>
     <r>
       <rPr>
@@ -2005,7 +2034,10 @@
         <rFont val="游ゴシック体"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">模試を。
+      <t xml:space="preserve">だけ。片手で答えられるので、通勤電車の中やちょっとした待ち時間に最適です
+・答えた直後に正解と簡単な解説が出るので、その場で確認でき、記憶に残りやすくなります
+・苦手なテーマは論点ごとの正答率でひと目でわかります
+・繰り返し解くことで、まだ解いていない問題と前回間違えた問題が優先して出題され、弱点を少しずつカバーできます
 ■ こんな方に
 ・まとまった勉強時間がとれない社会人の方
 ・過去問を解きっぱなしにしてしまう方
@@ -2256,6 +2288,25 @@
   </si>
   <si>
     <t xml:space="preserve">合格保証などの表現は使わない。実装済みの機能だけを書く</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：冒頭に「通勤電車の中で、スマホで勉強」の項目を追加</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">T6</t>
@@ -6382,19 +6433,19 @@
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
     </row>
-    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
         <v>106</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>108</v>
       </c>
       <c r="D4" s="8" t="n">
         <f aca="false">LEN(C4)</f>
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="E4" s="8" t="n">
         <v>170</v>
@@ -6404,17 +6455,19 @@
       </c>
       <c r="G4" s="10"/>
       <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
+      <c r="I4" s="8" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D5" s="8" t="n">
         <f aca="false">LEN(C5)</f>
@@ -6424,7 +6477,7 @@
         <v>100</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G5" s="10"/>
       <c r="H5" s="8"/>
@@ -6432,37 +6485,39 @@
     </row>
     <row r="6" customFormat="false" ht="408.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D6" s="8" t="n">
         <f aca="false">LEN(C6)</f>
-        <v>624</v>
+        <v>814</v>
       </c>
       <c r="E6" s="8" t="n">
         <v>4000</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
+      <c r="I6" s="8" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D7" s="8" t="n">
         <f aca="false">LEN(C7)</f>
@@ -6478,23 +6533,23 @@
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D8" s="8" t="n">
         <f aca="false">LEN(C8)</f>
         <v>41</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G8" s="10"/>
       <c r="H8" s="8"/>
@@ -6502,23 +6557,23 @@
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D9" s="8" t="n">
         <f aca="false">LEN(C9)</f>
         <v>41</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G9" s="10"/>
       <c r="H9" s="8"/>
@@ -6526,7 +6581,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="12" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -6563,7 +6618,7 @@
         <v>47</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>25</v>
@@ -6577,13 +6632,13 @@
     </row>
     <row r="2" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D2" s="10"/>
       <c r="E2" s="8"/>
@@ -6591,13 +6646,13 @@
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="8"/>
@@ -6605,13 +6660,13 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="8"/>
@@ -6619,13 +6674,13 @@
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="8"/>
@@ -6633,13 +6688,13 @@
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="8"/>
@@ -6647,13 +6702,13 @@
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="8"/>
@@ -6661,13 +6716,13 @@
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="8"/>
@@ -6675,13 +6730,13 @@
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="8"/>
@@ -6689,13 +6744,13 @@
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="8"/>
@@ -6703,13 +6758,13 @@
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="8"/>
@@ -6746,209 +6801,209 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>

--- a/design/デザイン案.xlsx
+++ b/design/デザイン案.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="229">
   <si>
     <r>
       <rPr>
@@ -72,7 +72,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">v2</t>
+      <t xml:space="preserve">v3</t>
     </r>
     <r>
       <rPr>
@@ -868,6 +868,42 @@
   </si>
   <si>
     <t xml:space="preserve">不動産（家の屋根）のモチーフで宅建と分かる案。下の金帯に「宅建模試」</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：採用（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">assets/icon.png </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に反映）</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">I5</t>
@@ -1332,6 +1368,76 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">と合わせる）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：採用。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">App Store Connect </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B-6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を登録</t>
     </r>
   </si>
   <si>
@@ -2340,29 +2446,116 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">https://icurate.jp/apps/takken/support</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（案）</t>
-    </r>
+    <t xml:space="preserve">https://icurate.jp/takken-support/</t>
   </si>
   <si>
     <t xml:space="preserve">—</t>
   </si>
   <si>
-    <t xml:space="preserve">公開するページを決めてから入れる</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">WordPress </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の固定ページ（スラッグ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">takken-support</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">docs/web/support.html </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を貼る</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">URL </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">icurate.jp/takken-support/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に決定</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">T8</t>
@@ -2387,26 +2580,113 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">https://icurate.jp/apps/takken/privacy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（案）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">下のプライバシーポリシーを掲載するページ</t>
+    <t xml:space="preserve">https://icurate.jp/takken-privacy/</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">WordPress </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の固定ページ（スラッグ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">takken-privacy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">docs/web/privacy.html </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を貼る</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">URL </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">icurate.jp/takken-privacy/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に決定</t>
+    </r>
   </si>
   <si>
     <r>
@@ -2885,7 +3165,41 @@
         <rFont val="游ゴシック体"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">年（月）（日）制定</t>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日 制定</t>
     </r>
   </si>
   <si>
@@ -5808,18 +6122,20 @@
       </c>
       <c r="E5" s="10"/>
       <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="G5" s="8" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="139.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E6" s="10"/>
       <c r="F6" s="8"/>
@@ -5827,14 +6143,14 @@
     </row>
     <row r="7" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E7" s="10"/>
       <c r="F7" s="8"/>
@@ -5877,16 +6193,16 @@
         <v>22</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>25</v>
@@ -5900,14 +6216,14 @@
     </row>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E2" s="8"/>
       <c r="F2" s="8"/>
@@ -5917,20 +6233,20 @@
     </row>
     <row r="3" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G3" s="10"/>
       <c r="H3" s="8"/>
@@ -5938,20 +6254,20 @@
     </row>
     <row r="4" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G4" s="10"/>
       <c r="H4" s="8"/>
@@ -5959,20 +6275,20 @@
     </row>
     <row r="5" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G5" s="10"/>
       <c r="H5" s="8"/>
@@ -5980,20 +6296,20 @@
     </row>
     <row r="6" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="8"/>
@@ -6001,20 +6317,20 @@
     </row>
     <row r="7" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G7" s="10"/>
       <c r="H7" s="8"/>
@@ -6022,20 +6338,20 @@
     </row>
     <row r="8" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G8" s="10"/>
       <c r="H8" s="8"/>
@@ -6043,37 +6359,39 @@
     </row>
     <row r="9" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
       <c r="G9" s="10"/>
       <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
+      <c r="I9" s="8" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="8"/>
@@ -6081,20 +6399,20 @@
     </row>
     <row r="11" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G11" s="10"/>
       <c r="H11" s="8"/>
@@ -6102,20 +6420,20 @@
     </row>
     <row r="12" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G12" s="10"/>
       <c r="H12" s="8"/>
@@ -6123,20 +6441,20 @@
     </row>
     <row r="13" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G13" s="10"/>
       <c r="H13" s="8"/>
@@ -6144,20 +6462,20 @@
     </row>
     <row r="14" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G14" s="10"/>
       <c r="H14" s="8"/>
@@ -6165,20 +6483,20 @@
     </row>
     <row r="15" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G15" s="10"/>
       <c r="H15" s="8"/>
@@ -6186,14 +6504,14 @@
     </row>
     <row r="16" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
@@ -6203,20 +6521,20 @@
     </row>
     <row r="17" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G17" s="10"/>
       <c r="H17" s="8"/>
@@ -6224,20 +6542,20 @@
     </row>
     <row r="18" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G18" s="10"/>
       <c r="H18" s="8"/>
@@ -6245,20 +6563,20 @@
     </row>
     <row r="19" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G19" s="10"/>
       <c r="H19" s="8"/>
@@ -6266,20 +6584,20 @@
     </row>
     <row r="20" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G20" s="10"/>
       <c r="H20" s="8"/>
@@ -6287,20 +6605,20 @@
     </row>
     <row r="21" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G21" s="10"/>
       <c r="H21" s="8"/>
@@ -6308,20 +6626,20 @@
     </row>
     <row r="22" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G22" s="10"/>
       <c r="H22" s="8"/>
@@ -6361,19 +6679,19 @@
         <v>21</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>25</v>
@@ -6387,13 +6705,13 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D2" s="8" t="n">
         <f aca="false">LEN(C2)</f>
@@ -6403,7 +6721,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G2" s="10"/>
       <c r="H2" s="8"/>
@@ -6411,13 +6729,13 @@
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D3" s="8" t="n">
         <f aca="false">LEN(C3)</f>
@@ -6427,7 +6745,7 @@
         <v>30</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G3" s="10"/>
       <c r="H3" s="8"/>
@@ -6435,13 +6753,13 @@
     </row>
     <row r="4" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D4" s="8" t="n">
         <f aca="false">LEN(C4)</f>
@@ -6451,23 +6769,23 @@
         <v>170</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G4" s="10"/>
       <c r="H4" s="8"/>
       <c r="I4" s="8" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D5" s="8" t="n">
         <f aca="false">LEN(C5)</f>
@@ -6477,7 +6795,7 @@
         <v>100</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G5" s="10"/>
       <c r="H5" s="8"/>
@@ -6485,13 +6803,13 @@
     </row>
     <row r="6" customFormat="false" ht="408.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D6" s="8" t="n">
         <f aca="false">LEN(C6)</f>
@@ -6501,23 +6819,23 @@
         <v>4000</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="8"/>
       <c r="I6" s="8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D7" s="8" t="n">
         <f aca="false">LEN(C7)</f>
@@ -6533,55 +6851,59 @@
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D8" s="8" t="n">
         <f aca="false">LEN(C8)</f>
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>129</v>
       </c>
       <c r="G8" s="10"/>
       <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
+      <c r="I8" s="8" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D9" s="8" t="n">
         <f aca="false">LEN(C9)</f>
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>131</v>
+        <v>128</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>134</v>
       </c>
       <c r="G9" s="10"/>
       <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
+      <c r="I9" s="8" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="12" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -6615,10 +6937,10 @@
         <v>21</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>25</v>
@@ -6632,13 +6954,13 @@
     </row>
     <row r="2" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D2" s="10"/>
       <c r="E2" s="8"/>
@@ -6646,13 +6968,13 @@
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="8"/>
@@ -6660,13 +6982,13 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="8"/>
@@ -6674,13 +6996,13 @@
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="8"/>
@@ -6688,13 +7010,13 @@
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="8"/>
@@ -6702,13 +7024,13 @@
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="8"/>
@@ -6716,13 +7038,13 @@
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="8"/>
@@ -6730,13 +7052,13 @@
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="8"/>
@@ -6744,13 +7066,13 @@
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="8"/>
@@ -6758,13 +7080,13 @@
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="8"/>
@@ -6801,209 +7123,209 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>

--- a/design/デザイン案.xlsx
+++ b/design/デザイン案.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="230">
   <si>
     <r>
       <rPr>
@@ -3130,8 +3130,42 @@
         <rFont val="游ゴシック体"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">所在地：東京都港区（番地を記入）
-メール：</t>
+      <t xml:space="preserve">所在地：〒</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">108-0075 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">東京都港区港南</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3-5-10-2902
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">メール：</t>
     </r>
     <r>
       <rPr>
@@ -3141,6 +3175,25 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">info@icurate.jp</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：所在地を記入</t>
     </r>
   </si>
   <si>
@@ -7064,7 +7117,7 @@
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
     </row>
-    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
         <v>162</v>
       </c>
@@ -7076,17 +7129,19 @@
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
+      <c r="F10" s="8" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="8"/>
@@ -7123,209 +7178,209 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>

--- a/design/デザイン案.xlsx
+++ b/design/デザイン案.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="229">
   <si>
     <r>
       <rPr>
@@ -2446,7 +2446,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">https://icurate.jp/takken-support/</t>
+    <t xml:space="preserve">https://apps.icurate.jp/takken/support/</t>
   </si>
   <si>
     <t xml:space="preserve">—</t>
@@ -2455,53 +2455,44 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">WordPress </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の固定ページ（スラッグ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">takken-support</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">docs/web/support.html </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を貼る</t>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">学習アプリ事業のサイト（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">site/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">apps.icurate.jp </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に公開）</t>
     </r>
   </si>
   <si>
@@ -2546,15 +2537,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">icurate.jp/takken-support/ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">に決定</t>
+      <t xml:space="preserve">apps.icurate.jp/takken/support/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に変更（事業別サイト）</t>
     </r>
   </si>
   <si>
@@ -2580,60 +2571,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">https://icurate.jp/takken-privacy/</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">WordPress </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の固定ページ（スラッグ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">takken-privacy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">docs/web/privacy.html </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を貼る</t>
-    </r>
+    <t xml:space="preserve">https://apps.icurate.jp/takken/privacy/</t>
   </si>
   <si>
     <r>
@@ -2677,15 +2615,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">icurate.jp/takken-privacy/ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">に決定</t>
+      <t xml:space="preserve">apps.icurate.jp/takken/privacy/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に変更（事業別サイト）</t>
     </r>
   </si>
   <si>
@@ -6914,12 +6852,12 @@
       </c>
       <c r="D8" s="8" t="n">
         <f aca="false">LEN(C8)</f>
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="9" t="s">
         <v>129</v>
       </c>
       <c r="G8" s="10"/>
@@ -6940,23 +6878,23 @@
       </c>
       <c r="D9" s="8" t="n">
         <f aca="false">LEN(C9)</f>
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>134</v>
+      <c r="F9" s="9" t="s">
+        <v>129</v>
       </c>
       <c r="G9" s="10"/>
       <c r="H9" s="8"/>
       <c r="I9" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -6993,7 +6931,7 @@
         <v>48</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>25</v>
@@ -7007,13 +6945,13 @@
     </row>
     <row r="2" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="C2" s="9" t="s">
         <v>139</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>140</v>
       </c>
       <c r="D2" s="10"/>
       <c r="E2" s="8"/>
@@ -7021,13 +6959,13 @@
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="C3" s="9" t="s">
         <v>142</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>143</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="8"/>
@@ -7035,13 +6973,13 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>145</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>146</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="8"/>
@@ -7049,13 +6987,13 @@
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="C5" s="9" t="s">
         <v>148</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>149</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="8"/>
@@ -7063,13 +7001,13 @@
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="C6" s="9" t="s">
         <v>151</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>152</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="8"/>
@@ -7077,13 +7015,13 @@
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="C7" s="9" t="s">
         <v>154</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>155</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="8"/>
@@ -7091,13 +7029,13 @@
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="C8" s="9" t="s">
         <v>157</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>158</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="8"/>
@@ -7105,13 +7043,13 @@
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="C9" s="9" t="s">
         <v>160</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>161</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="8"/>
@@ -7119,29 +7057,29 @@
     </row>
     <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="C10" s="9" t="s">
         <v>163</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>164</v>
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="8"/>
       <c r="F10" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="C11" s="8" t="s">
         <v>167</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>168</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="8"/>
@@ -7178,209 +7116,209 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>175</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="C2" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="D2" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="F2" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="G2" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="H2" s="13" t="s">
         <v>183</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="C3" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="E3" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="F3" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="G3" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="H3" s="13" t="s">
         <v>191</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="E4" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="F4" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="G4" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="H4" s="13" t="s">
         <v>199</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="C5" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="D5" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="E5" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="G5" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="H5" s="13" t="s">
         <v>207</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="C6" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="D6" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="E6" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="F6" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="G6" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="H6" s="13" t="s">
         <v>215</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="C7" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="D7" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="E7" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="F7" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="G7" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="H7" s="13" t="s">
         <v>223</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>

--- a/design/デザイン案.xlsx
+++ b/design/デザイン案.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="230">
   <si>
     <r>
       <rPr>
@@ -72,7 +72,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">v3</t>
+      <t xml:space="preserve">v4</t>
     </r>
     <r>
       <rPr>
@@ -1234,27 +1234,19 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">論点ごとの直近</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">問の正答率マップ</t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">47</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">論点の正答率をタイルで表示</t>
     </r>
   </si>
   <si>
@@ -1395,49 +1387,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">App Store Connect </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">に </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B-1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B-6 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を登録</t>
+      <t xml:space="preserve">v4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：音声ボタンを消した最新画面で撮り直し</t>
     </r>
   </si>
   <si>
@@ -1454,6 +1412,25 @@
   </si>
   <si>
     <t xml:space="preserve">B-5</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：論点マップを新しいタイル表示の画面に差し替え</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">B-6</t>
@@ -2200,7 +2177,41 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">回分
-・宅建業法・権利関係・法令上の制限・税その他を、本試験と同じ比率で出題します
+・収録は○</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">問。宅建業法・権利関係・法令上の制限・税その他を、本試験と同じ比率で出題します
 ・</t>
     </r>
     <r>
@@ -2293,24 +2304,24 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">問の順で復習します
-・論点ごとの直近</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">問の正答率を色で表示。苦手がひと目でわかります
+・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">47</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">論点をタイルで表示。正答率が上がるほど緑が濃くなり、苦手がひと目でわかります
 ■ 合格の見込み
 ・直近の正答率から、</t>
     </r>
@@ -2403,15 +2414,49 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">v2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：冒頭に「通勤電車の中で、スマホで勉強」の項目を追加</t>
+      <t xml:space="preserve">v4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：収録約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">問・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">47</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">論点のタイル表示を追記</t>
     </r>
   </si>
   <si>
@@ -6317,7 +6362,7 @@
       <c r="D7" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="8" t="s">
         <v>72</v>
       </c>
       <c r="F7" s="9" t="s">
@@ -6462,7 +6507,7 @@
       <c r="D14" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="8" t="s">
         <v>72</v>
       </c>
       <c r="F14" s="9" t="s">
@@ -6470,11 +6515,13 @@
       </c>
       <c r="G14" s="10"/>
       <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
+      <c r="I14" s="8" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="9" t="s">
@@ -6495,11 +6542,11 @@
     </row>
     <row r="16" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>53</v>
@@ -6512,11 +6559,11 @@
     </row>
     <row r="17" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>55</v>
@@ -6533,11 +6580,11 @@
     </row>
     <row r="18" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>59</v>
@@ -6554,11 +6601,11 @@
     </row>
     <row r="19" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>63</v>
@@ -6575,11 +6622,11 @@
     </row>
     <row r="20" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>67</v>
@@ -6596,16 +6643,16 @@
     </row>
     <row r="21" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="8" t="s">
         <v>72</v>
       </c>
       <c r="F21" s="9" t="s">
@@ -6617,11 +6664,11 @@
     </row>
     <row r="22" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>75</v>
@@ -6670,19 +6717,19 @@
         <v>21</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>25</v>
@@ -6696,13 +6743,13 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D2" s="8" t="n">
         <f aca="false">LEN(C2)</f>
@@ -6712,7 +6759,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G2" s="10"/>
       <c r="H2" s="8"/>
@@ -6720,13 +6767,13 @@
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D3" s="8" t="n">
         <f aca="false">LEN(C3)</f>
@@ -6736,7 +6783,7 @@
         <v>30</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G3" s="10"/>
       <c r="H3" s="8"/>
@@ -6744,13 +6791,13 @@
     </row>
     <row r="4" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D4" s="8" t="n">
         <f aca="false">LEN(C4)</f>
@@ -6760,23 +6807,23 @@
         <v>170</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G4" s="10"/>
       <c r="H4" s="8"/>
       <c r="I4" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D5" s="8" t="n">
         <f aca="false">LEN(C5)</f>
@@ -6786,7 +6833,7 @@
         <v>100</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G5" s="10"/>
       <c r="H5" s="8"/>
@@ -6794,39 +6841,39 @@
     </row>
     <row r="6" customFormat="false" ht="408.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D6" s="8" t="n">
         <f aca="false">LEN(C6)</f>
-        <v>814</v>
+        <v>836</v>
       </c>
       <c r="E6" s="8" t="n">
         <v>4000</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="8"/>
       <c r="I6" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D7" s="8" t="n">
         <f aca="false">LEN(C7)</f>
@@ -6842,59 +6889,59 @@
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D8" s="8" t="n">
         <f aca="false">LEN(C8)</f>
         <v>39</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G8" s="10"/>
       <c r="H8" s="8"/>
       <c r="I8" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D9" s="8" t="n">
         <f aca="false">LEN(C9)</f>
         <v>39</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G9" s="10"/>
       <c r="H9" s="8"/>
       <c r="I9" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -6931,7 +6978,7 @@
         <v>48</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>25</v>
@@ -6945,13 +6992,13 @@
     </row>
     <row r="2" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D2" s="10"/>
       <c r="E2" s="8"/>
@@ -6959,13 +7006,13 @@
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="8"/>
@@ -6973,13 +7020,13 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="8"/>
@@ -6987,13 +7034,13 @@
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="8"/>
@@ -7001,13 +7048,13 @@
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="8"/>
@@ -7015,13 +7062,13 @@
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="8"/>
@@ -7029,13 +7076,13 @@
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="8"/>
@@ -7043,13 +7090,13 @@
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="8"/>
@@ -7057,29 +7104,29 @@
     </row>
     <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="8"/>
       <c r="F10" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="8"/>
@@ -7116,209 +7163,209 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>

--- a/design/デザイン案.xlsx
+++ b/design/デザイン案.xlsx
@@ -72,7 +72,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">v4</t>
+      <t xml:space="preserve">v5</t>
     </r>
     <r>
       <rPr>
@@ -1421,15 +1421,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">v4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：論点マップを新しいタイル表示の画面に差し替え</t>
+      <t xml:space="preserve">v5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：タイルに「解いた数／収録数・正解数」を表示した画面に差し替え</t>
     </r>
   </si>
   <si>
